--- a/artfynd/A 59532-2025 artfynd.xlsx
+++ b/artfynd/A 59532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>74207722</v>
       </c>
       <c r="B2" t="n">
-        <v>107189</v>
+        <v>107718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75177615</v>
+        <v>74119204</v>
       </c>
       <c r="B3" t="n">
-        <v>102913</v>
+        <v>101896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E5h 1121. SOM: Ulmus glabra. LEG: Thomas Karlsson, Tord Holm, Signe Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E5h 1121. SOM: Chrysosplenium alternifolium. LEG: Thomas Karlsson, Tord Holm, Signe Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skogskant</t>
+          <t>Alkärr</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -890,6 +890,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75177615</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103402</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L20 Sjötorp västra gdn 550 m SO, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>484828</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6423745</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1982-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7E5h 1121. SOM: Ulmus glabra. LEG: Thomas Karlsson, Tord Holm, Signe Karlsson</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Skogskant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 59532-2025 artfynd.xlsx
+++ b/artfynd/A 59532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74207722</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74119204</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75177615</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>